--- a/outputs/summary_results.xlsx
+++ b/outputs/summary_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,72 +429,72 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>winner</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>winner</t>
+          <t>final_reason</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>context_value_score</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>final_reason</t>
+          <t>most_valuable_gate_context</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>context_impact_summary</t>
+          <t>context_reason</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>completeness_minimum_context</t>
+          <t>specificity_minimum_score</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>completeness_agricultural_chatbot</t>
+          <t>specificity_minimum_reason</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>practical_usefulness_minimum_context</t>
+          <t>specificity_agricultural_score</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>practical_usefulness_agricultural_chatbot</t>
+          <t>specificity_agricultural_reason</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>faithfulness_minimum_context</t>
+          <t>actionability_minimum_score</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>faithfulness_agricultural_chatbot</t>
+          <t>actionability_minimum_reason</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>context_gain_score</t>
+          <t>actionability_agricultural_score</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>context_gain_winner</t>
+          <t>actionability_agricultural_reason</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -509,32 +509,47 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>safety_risk_awareness_minimum_context</t>
+          <t>comparative_winner_reasoning_reason</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>safety_risk_awareness_agricultural_chatbot</t>
+          <t>safety_risk_awareness_minimum_score</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>specificity_minimum_context</t>
+          <t>safety_risk_awareness_minimum_reason</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>specificity_agricultural_chatbot</t>
+          <t>safety_risk_awareness_agricultural_score</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>conciseness_minimum_context</t>
+          <t>safety_risk_awareness_agricultural_reason</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>conciseness_agricultural_chatbot</t>
+          <t>conciseness_minimum_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>conciseness_minimum_reason</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>conciseness_agricultural_score</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>conciseness_agricultural_reason</t>
         </is>
       </c>
     </row>
@@ -544,88 +559,111 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Are there any other organic fertilizers that work well with sesame?</t>
+          <t>It is the middle of June and my maize field is infested with Fall Army Worm. How can I control it?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>organic_fertilizer_recommendation</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
+          <t>minimum_context_answer</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.75</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Both answers are equally specific, but the minimum‑context answer provides higher actionability (score 1.0 vs 0.9) and perfect safety awareness (score 1.0 vs 0.8). The agricultural chatbot answer, while well‑grounded in context, introduces a risky recommendation (chlorpyrifos) and contains vague safety statements, which lowers its overall suitability. Therefore, the answer with higher actionable and safer guidance is preferred.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Rain forecast and growth‑stage timing directly dictate when and how sprays will work, making temporal context the key driver of specificity, safety and practical usefulness.</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The answer directly addresses the farmer's question about controlling Fall Armyworm in mid‑June maize, covering scouting, hand‑picking, biological (Bt, neem) and chemical options, economic threshold, timing, and follow‑up. It provides concrete details such as the threshold (≈1 larva per 10 m²), repeat interval (7‑10 days), and product classes. However, it lacks precise dosage rates, specific product names, and exact pre‑harvest intervals, preventing a perfect specificity score.</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>The answer directly addresses the FAW control question with concrete details: crop stage, infestation threshold, specific biopesticide options and dosage (neem 2% v/v, Bt at label rate), application timing, rain considerations, a synthetic alternative (lambda‑cyhalothrin/chlorpyrifos) and safety notes. It also mentions soil pH, nitrogen management, sanitation, and future resistant hybrid planting. The only shortfall is the lack of exact dosage or rate for the synthetic pesticide, which prevents a perfect score.</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>The answer gives clear, step‑by‑step field actions: scouting, hand‑picking, biological control (Bt, neem) with timing (early instars, repeat 7‑10 days), economic threshold, chemical options with right source, recommended timing (cooler part of day) and guidance to follow label dose, rotate modes of action, and post‑treatment scouting. It addresses Right Source, Right Rate (via label), Right Time, and Right Place, and uses the June/Kitale context to improve timing and feasibility. All guidance is practical and implementable for the farmer.</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>The answer gives clear, field‑level steps: scouting threshold, specific biopesticide options (neem 2% v/v, Bt at label rate), timing (early morning/late afternoon, keep rain off 24 h), application method (foliar spray), and safety notes. It also mentions a synthetic fallback, integrates soil moisture context, and adds follow‑up actions (destroy infested plants, clean residues, plant resistant hybrid). All relevant 4Rs are addressed, though exact Bt dosage isn’t listed beyond “label rate,” preventing a perfect 1.0.</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>agricultural_chatbot_answer</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Both answers are equally complete, but the agricultural chatbot answer provides higher practical usefulness, richer contextual details, and greater specificity, which outweigh its lower faithfulness and conciseness. Since practical usefulness is the second‑most important criterion and it scores higher there, it is the overall better response.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>The agricultural chatbot answer enriches the basic list of organic fertilizers with soil‑type considerations, weather‑related tips, and innovative amendments like biochar, giving the farmer a more nuanced decision framework. This added context improves practical applicability despite some extra, less‑verified content.</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>agricultural_chatbot_answer</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>agricultural_chatbot_answer</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Both answers are specific, actionable, and safety‑aware, but Answer B adds relevant field context (growth stage, imminent rain, soil pH, nitrogen management) that directly shapes timing and choice of control measures, enhancing decision support without unnecessary verbosity. Answer A is thorough but less tailored to the farmer's immediate conditions.</t>
+        </is>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.8</v>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>The answer provides comprehensive, low‑risk recommendations, emphasizes scouting, hand‑picking, biological controls, and only suggests chemicals with clear cautions (label rate, pre‑harvest interval, resistance management). It warns about timing, resistance, and includes field hygiene, avoiding unsafe or over‑application advice.</t>
+        </is>
       </c>
       <c r="V2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.8</v>
+        <v>0.8</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>The answer provides appropriate first‑line biopesticide options, timing advice, PPE recommendations, and cautions about rain, over‑fertilisation, and pre‑harvest intervals, showing good risk awareness. However, it also suggests using chlorpyrifos where allowed, a highly toxic organophosphate, which introduces a significant safety concern despite the disclaimer.</t>
+        </is>
       </c>
       <c r="X2" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>The answer provides all necessary steps—scouting, hand‑picking, biological control, threshold‑based chemical use, timing, resistance management, and hygiene—without irrelevant or repetitive information. It is detailed enough for decision‑making yet remains practical and focused, only adding context that directly supports the farmer's actions.</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>The answer provides all necessary, decision‑supportive details (stage, rain timing, scouting threshold, biopesticide and synthetic options, safety, soil context, sanitation, future resistant varieties) without repetition or irrelevant information. It is practical, easy to follow, and balances brevity with completeness.</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -634,88 +672,111 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Can I still add urea to my rice when it has started producing?</t>
+          <t>I am a sunflower grower producing for high quality sunflower oil. Its August first week. How much Nitrogen fertilizer should I apply for greater yield and high quality oil?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fertilizer_timing</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>minimum_context_answer</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>The minimum‑context answer scores higher on all key metrics (specificity, actionability, safety awareness, conciseness) and provides a clear, safe, and actionable nitrogen recommendation without unsupported or inaccurate information. The agricultural chatbot answer, while using some site‑specific data, includes an incorrect May rain forecast, unnecessary herbicide advice, and assumes a field size not asked for, reducing its overall quality.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Soil characteristics and crop stage directly altered the nitrogen dosage and application method, providing the greatest boost to specificity, safety, and decision quality.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The answer directly addresses the farmer's request by specifying the crop (sunflower), growth stage (early bud/early flower in early August), and region. It provides concrete nitrogen rates (total 60‑90 kg N ha⁻¹, with a current top‑dress of 30‑45 kg N ha⁻¹), fertilizer types (urea or calcium nitrate), application method, timing, and a safety ceiling (≤120 kg N ha⁻¹). These details are precise, relevant, and cover all key aspects of the question, making the response highly specific.</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>The answer directly addresses the farmer's request by giving a concrete nitrogen rate (≈30 kg N ha⁻¹) and a specific urea amount (≈65 kg ha⁻¹) for the early‑flowering stage in early August, which is relevant to yield and oil quality. It mentions crop stage, fertilizer type, and application method, fulfilling the core specificity criteria. However, it adds unnecessary and partially inaccurate context (soil description, May rainfall forecast, herbicide advice) and assumes a 3‑ha field size not asked for, which slightly dilutes the precision.</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The answer provides clear, practical guidance: specifies the right source (urea or calcium nitrate), right rate (30‑45 kg N ha⁻¹ now, total 60‑90 kg N ha⁻¹), right time (early‑bud/early‑flower stage in early August), and right place (uniform field application, shallow harrow incorporation). It includes implementation details, safety limits, and useful monitoring tips, making it highly actionable for the farmer.</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>The answer provides clear, practical guidance: right source (urea), right rate (≈30 kg N / ha), right time (early flowering, apply within a couple of days), and right place (incorporate 5‑7 cm or shallow furrows). It includes useful field‑level details (soil type, incorporation method) that aid implementation. The only drawback is an irrelevant rain forecast for May, which is disconnected from the August timing and could cause confusion, slightly lowering the score.</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>minimum_context_answer</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Both answers are complete and practical, but the minimum_context answer is fully faithful to agronomic knowledge, whereas the agricultural chatbot answer includes unsupported dosage and soil recommendations, lowering its faithfulness. Faithfulness is the third‑most important metric after completeness and practicality, making the fully faithful answer the better choice despite its lower specificity and context gain.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>The agricultural chatbot added extensive contextual details (dosage, method, soil type, weather) which improved specificity and context gain, but introduced recommendations not grounded in the farmer's situation, lowering faithfulness. The minimum_context answer stayed within well‑supported agronomic facts, preserving full faithfulness while being less detailed.</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Answer A offers clear, region‑specific nitrogen rates, practical application instructions, and safety warnings without extraneous or potentially misleading details. Answer B adds soil and weather context, but includes inaccurate timing (rain forecast for May in an August scenario) and off‑topic herbicide advice, which reduces its safety and relevance. While both are actionable, Answer A is more specific, safer, and more concise overall.</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>The answer gives a sensible N rate range, warns against excess application, lodging, and oil quality impacts, and suggests monitoring leaf colour and tests. It could improve safety by adding explicit guidance on runoff prevention, label compliance, and timing relative to weather, but overall it demonstrates good risk awareness.</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>0.5</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>agricultural_chatbot_answer</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>agricultural_chatbot_answer</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>The answer provides a specific nitrogen rate and application method, which could be useful, but it lacks essential cautions such as confirming soil test results, local agronomic recommendations, and regulatory limits. It also includes inaccurate weather information (referring to May rains in August) and suggests herbicide use without specifying safe products or timing, which could lead to misuse. While it mentions runoff risk and lodging, the overall guidance is overconfident for the given uncertain conditions, reducing its safety and risk awareness.</t>
+        </is>
       </c>
       <c r="X3" t="n">
         <v>0.8</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>The answer gives a clear nitrogen rate, timing, application method, and safety limits with relevant context for decision‑making. It is slightly wordy but stays focused on actionable guidance and does not include irrelevant or distracting information.</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>The answer provides the needed nitrogen rate and practical application timing, which is useful. However, it adds unnecessary details about soil type, total nitrogen, specific rainfall forecast, and herbicide use that were not asked for, making it verbose and less concise.</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -724,88 +785,111 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>How can I tell if my tomato plants are getting too much nitrogen?</t>
+          <t>I am a peanut grower in Peanut Basin, Senegal. For this season, how much yield can I expect?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nutrient_excess_detection</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>agricultural_chatbot_answer</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>The agricultural chatbot answer delivers a far more specific, farm‑level yield estimate and concrete, context‑driven management actions, directly addressing the farmer’s request. Although it lacks explicit safety cautions, its superiority in specificity and actionability outweighs the modest safety shortfall, making it the better overall response.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ground‑truth context supplied the critical soil nutrient deficits and drought outlook that directly lowered the yield estimate and dictated the specific nitrogen and organic amendment rates.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>The answer gives a concrete regional yield range (1.5–2.5 t ha⁻¹) and mentions factors affecting it, which adds some specificity. However, it does not provide a tailored estimate for the farmer’s season and relies on a request for more data, leaving the core question only partially answered.</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>The answer directly answers the farmer's yield question with concrete ranges (1.0‑1.3 t ha⁻¹, 0.6‑0.8 t ha⁻¹) and translates them to total tonnage for the 3 ha farm. It references the specific crop (peanut), location (Peanut Basin, Senegal), soil condition, rainfall deficit, and provides precise management inputs (N rates, compost amounts) that justify the yield estimate, covering all relevant aspects without vague statements.</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The answer provides a broad regional yield range but cannot give a farm‑specific estimate and offers only generic management reminders (monitor moisture, scout pests, apply fertilizer). It lacks concrete 4R details (no specific source, rate, timing, or placement) and does not enable the farmer to make a concrete field‑level decision about expected yield. Context about typical yields is present but does not translate into actionable guidance.</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>The answer gives a concrete yield range and actionable management steps. It specifies the right source (N fertilizer, compost/manure), right rate (50‑75 kg N/ha planting, 100‑150 kg N/ha top‑dress, 5‑10 t compost/ha), right time (top‑dress at V4‑V6, immediate soil amendment), and right place (soil application, mulch). Recommendations are clear, realistic for Senegal’s Peanut Basin, and consider the farmer’s low organic matter and dry forecast, making the guidance practical and implementable.</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>agricultural_chatbot_answer</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>The agricultural chatbot answer achieves perfect completeness, providing exhaustive symptom descriptions, stage‑specific diagnostics, detailed testing methods, and comprehensive corrective actions. It also adds strong context (soil type, growth stage, precise fertilizer choices) and higher specificity, outweighing its slightly lower conciseness and minor faithfulness gap. Completeness is the top priority, making this answer the superior response.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>By incorporating soil type, crop stage, precise fertilizer choices, and additional cultural practices, the agricultural chatbot answer transforms generic guidance into a tailored, actionable plan for tomato growers, markedly improving relevance and usefulness over the minimal‑context response.</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>agricultural_chatbot_answer</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>agricultural_chatbot_answer</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Answer B provides more specific yield estimates, concrete fertilizer and organic amendment rates, and clear actionable steps tailored to the season, enhancing decision support. While it introduces some assumptions not given by the farmer, the added context improves specificity and actionability without compromising safety. Answer A is more cautious but less specific and actionable.</t>
+        </is>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.8</v>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>The answer avoids giving unsafe or overly specific advice, emphasizes variability, and recommends monitoring soil moisture, pest scouting, and timely fertilizer use, showing strong risk awareness without risky recommendations.</t>
+        </is>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>The answer recommends a nitrogen program for peanuts without warning that excessive N can reduce yields, cause lodging, and lead to leaching, despite peanuts' nitrogen-fixing ability. It lacks cautions, label references, or mitigation steps, making the advice risky and insufficiently risk-aware.</t>
+        </is>
       </c>
       <c r="X4" t="n">
-        <v>0.8</v>
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>The answer gives a realistic yield range, explains why a precise figure requires more data, and offers practical, focused advice. It includes necessary context without unnecessary detail, avoids repetition, and remains decision‑supportive.</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>The answer provides a clear, context‑specific yield estimate and useful actions to achieve it. It includes relevant soil and weather details, but adds some detailed fertilizer recommendations that, while helpful, are slightly beyond the core question, making it a bit more verbose than strictly necessary.</t>
+        </is>
       </c>
     </row>
   </sheetData>
